--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/CALIFORNIA_2024.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2024/CALIFORNIA_2024.xlsx
@@ -4992,7 +4992,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C258">
@@ -8034,7 +8034,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C427">
@@ -17142,7 +17142,7 @@
       </c>
       <c r="B933" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C933">
@@ -23730,7 +23730,7 @@
       </c>
       <c r="B1299" t="inlineStr">
         <is>
-          <t>Santa Ana Tlapacoya</t>
+          <t>Santa Ana Tlapacoyan</t>
         </is>
       </c>
       <c r="C1299">
@@ -26520,7 +26520,7 @@
       </c>
       <c r="B1454" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1454">
@@ -35898,7 +35898,7 @@
       </c>
       <c r="B1975" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1975">
